--- a/samples/QA知识库模板.xlsx
+++ b/samples/QA知识库模板.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,21 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E3F4F1"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +55,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,150 +423,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>问题</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>答案</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>相似问法</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>关键词</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>有几个颜色</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>亲，目前有黑色、白色、燕麦色三个颜色哦~</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>有什么颜色|颜色有哪些|几种颜色</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>颜色|黑色|白色|燕麦色</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>售前</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>多久发货</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>亲，付款后48小时内发货，节假日顺延哦~</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>什么时候发货|几天发货|发货时间</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>多久+发|什么时候+发|几天+发|明天+发|今天+发|发货</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>售前</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>怎么选尺码</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>亲，身高160-170建议M码，170-180建议L码，拿不准可以告诉我身高体重~</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>尺码怎么选|穿什么码|选多大的</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>尺码|什么码|多大码|身高+体重</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>售前</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>有没有优惠</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>亲，店铺现在满199减20，领券后下单更划算哦~</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>能便宜点吗|有优惠券吗|打折吗</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>优惠|便宜|券|打折|活动</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>售前</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>是正品吗</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>亲，本店为品牌官方店铺，所有商品均为正品，支持专柜验货~</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>保真吗|是不是正品</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>正品|保真|假货</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>售前</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>问题</t>
+          <t>列</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>答案</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>相似问法</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>品牌</t>
+          <t>说明</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>有几个颜色</t>
+          <t>问题</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>亲，目前有黑色、白色、燕麦色三个颜色哦~</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>有什么颜色|颜色有哪些|几种颜色</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>售前</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
+          <t>标准问法（必填）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>多久发货</t>
+          <t>答案</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>亲，付款后48小时内发货，节假日顺延哦~</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>什么时候发货|几天发货|发货时间</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>售前</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>命中后直接发给买家的话（必填）</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>怎么选尺码</t>
+          <t>相似问法</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>亲，身高160-170建议M码，170-180建议L码，拿不准可以告诉我身高体重~</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>尺码怎么选|穿什么码|选多大的</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>售前</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>其他问法，用 | 分隔</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>有没有优惠</t>
+          <t>关键词</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>亲，店铺现在满199减20，领券后下单更划算哦~</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>能便宜点吗|有优惠券吗|打折吗</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>售前</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>买家的话里出现这些词就命中，用 | 分隔多组；一组里用 + 连接表示都要出现，如：多久+发|发货。不需要模型</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>是正品吗</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>亲，本店为品牌官方店铺，所有商品均为正品，支持专柜验货~</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>保真吗|是不是正品</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>售前</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>售前/物流/售后等，可留空</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>品牌</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>只对某个品牌生效时填写，留空=所有店铺通用</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
